--- a/xlsx/AC-W.xlsx
+++ b/xlsx/AC-W.xlsx
@@ -18,7 +18,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AC-WP-L3" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AC-WP-L4" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AC-WP-L5" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_코드체계" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AC-W-M1" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AC-W-M2" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AC-W-M3" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_코드체계" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,7 +31,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -113,8 +116,28 @@
       <color rgb="FF1C1C1A"/>
       <sz val="15"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF1C4A41"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF1C4A41"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF1C4A41"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -146,6 +169,11 @@
         <fgColor rgb="FFF4EBE0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EFEC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -167,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -217,6 +245,44 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -583,7 +649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -610,6 +676,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -843,7 +910,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>단일 하지 칸막이</t>
+          <t>단일 벽체틀</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -879,7 +946,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>단일 하지 칸막이 (확대)</t>
+          <t>단일 벽체틀 (확대)</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -915,7 +982,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>이중 하지 칸막이</t>
+          <t>이중 벽체틀</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -951,7 +1018,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>이중 하지 칸막이 (분리 확대)</t>
+          <t>이중 벽체틀 (분리 확대)</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -987,7 +1054,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>이중 하지 칸막이 (질량 보강)</t>
+          <t>이중 벽체틀 (질량 보강)</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1012,367 +1079,495 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>AC-W-M1</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>유닛 조립형 · 내부벽</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>흡음 + 차음</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>아파트</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="n"/>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>같은 세대 내부와 맞닿은 벽</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>AC-W-M2</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>유닛 조립형 · 콘크리트 경계벽</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>차음</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>아파트</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="n"/>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>타세대 콘크리트 경계벽</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="20" t="inlineStr">
+        <is>
+          <t>AC-W-M3</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>유닛 조립형 · 건식 경계벽</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>차음 (기존 벽 보강)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>아파트</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="n"/>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t>주상복합 등 건식 경계벽</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>코드 체계</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>AC-WS-L?</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>구조벽면형 — 기존 구조체가 있는 면 (세대간벽 · 외벽 · 복도벽 · 코어벽)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>AC-WP-L?</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>칸막이형 — 구조체 없이 새로 세우는 실간벽 (양면 대칭)</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>LT</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>목재 하지 (Timber) — 투바이 각재</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>목재 벽체틀 (Timber) — 투바이 각재</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>LS</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>경량스터드 하지 (Steel) — 불연 요구 · 방화구획 · 감리 반려 현장</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>경량스터드 벽체틀 (Steel) — 불연 요구 · 방화구획 · 감리 반려 현장</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="inlineStr">
+        <is>
+          <t>AC-W-M?</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>유닛 조립형 — 아파트 · 오피스텔 전용. 작업장 선제작 후 현장 조립, 해체 · 재사용 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>표기 예</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>AC-WS-LT-3 / AC-WP-LS-4</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>절벽 구간</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>WS-L2 → L1 : 성능의 절벽 (이격 유무 — 차음 성립 여부가 갈림)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>WS-L3 → L2 : 구조의 절벽 (구조체 접촉 소멸 — 저역이 열리는 지점)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>WP-L3 → L2 : 구조의 절벽 (스터드 관통 전달 소멸 — 단일 → 이중)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>L5 → AC-B : 공법의 절벽 (직접 시공 상한 — 6면 독립계로 전환)</t>
-        </is>
-      </c>
-    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>설계 상한 · 공통 규칙</t>
+          <t>절벽 구간</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>· 이격 · 열간 분리 최대 50mm — 초과 시 수확체감. 두께가 더 필요하면 하지 규격 상향이 유리</t>
+          <t>WS-L2 → L1 : 성능의 절벽 (이격 유무 — 차음 성립 여부가 갈림)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>· 미네랄울 충진 최대 100T — 흡음은 100T에서 포화. 남는 공간은 f₀를 결정하는 거리로 작동</t>
+          <t>WS-L3 → L2 : 구조의 절벽 (구조체 접촉 소멸 — 저역이 열리는 지점)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>· 미네랄울은 소음원 쪽(구조체 면)에 밀착. 실내측 마감판 뒷면과 접촉 금지 — 제진 무효화</t>
+          <t>WP-L3 → L2 : 구조의 절벽 (스터드 관통 전달 소멸 — 단일 → 이중)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>· 마감판은 등급별 고정 — 같은 등급이면 WS · WP 어느 면이든 동일 구성 (4면 마감선 일관)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>· 그린글루는 L3부터 — 구조 전달이 지배적인 L1 · L2에서는 같은 예산을 중공층에 투입</t>
-        </is>
-      </c>
-    </row>
+          <t>L5 → AC-B : 공법의 절벽 (직접 시공 상한 — 6면 독립계로 전환)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>· 돌차음판은 WS 전 등급 구조체 면 + L5 마감판 사이 (WS · WP 공통)</t>
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>설계 상한 · 공통 규칙</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>· 삼중 구성 금지 — 공기층이 둘로 쪼개져 저역에서 15~20dB 악화</t>
+          <t>· 이격 · 열간 분리 최대 50mm — 초과 시 수확체감. 두께가 더 필요하면 벽체틀 규격 상향이 유리</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
+          <t>· 미네랄울 충진 최대 100T — 흡음은 100T에서 포화. 남는 공간은 f₀를 결정하는 거리로 작동</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>· 미네랄울은 소음원 쪽(구조체 면)에 밀착. 실내측 마감판 뒷면과 접촉 금지 — 제진 무효화</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>· 마감판은 등급별 고정 — 같은 등급이면 WS · WP 어느 면이든 동일 구성 (4면 마감선 일관)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>· 그린글루는 L3부터 — 구조 전달이 지배적인 L1 · L2에서는 같은 예산을 중공층에 투입</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>· 돌차음판은 WS 전 등급 구조체 면 + L5 마감판 사이 (WS · WP 공통)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>· 삼중 구성 금지 — 공기층이 둘로 쪼개져 저역에서 15~20dB 악화</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
           <t>· 실 단위 등급(AC-R) 우선 — 6면 중 한 면이라도 낮으면 그 면이 실 성능을 결정</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>공통 자재</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>규격</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>돌차음판</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>4T · 자체 점착 타입</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>WS 전 등급 구조체 면 / L5 마감판 사이</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>일반석고보드</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>9.5T</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>전 등급 1겹 (내측)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>차음석고보드</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>12.5T</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>전 등급 2겹 (외측) · F 시리즈와 자재 통일</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>미네랄울 보드</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>48K · 30T / 50T</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>KCC 또는 벽산 · 라이트필 031-604-3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>그린글루</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>L3 이상 · 약 0.6~0.8 튜브/㎡</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>고무패드</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>3T</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>상하부 런너 · 각재 뒷면 (L1 · L2)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>탄성 실란트</t>
+          <t>돌차음판</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4T · 자체 점착 타입</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>사방 단부 · 경화형 퍼티 금지</t>
+          <t>WS 전 등급 구조체 면 / L5 마감판 사이</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>투바이 각재</t>
+          <t>일반석고보드</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>30×30 / 30×67 / 38×89 / 38×140</t>
+          <t>9.5T</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>LT 계열</t>
+          <t>전 등급 1겹 (내측)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
+          <t>차음석고보드</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>12.5T</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>전 등급 2겹 (외측) · F 시리즈와 자재 통일</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>미네랄울 보온판 50K</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>50K · 50T · 450×1000</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>벽산 또는 KCC · 라이트필 031-604-3000 · 최소 두께 50T</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="56" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>그린글루</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>L3 이상 · 약 0.6~0.8 튜브/㎡</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>고무패드</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>3T</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>상하부 런너 · 각재 뒷면 (L1 · L2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="56" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>탄성 실란트</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>사방 단부 · 경화형 퍼티 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>투바이 각재</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>30×30 / 30×67 / 38×89 / 38×140</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>LT 계열</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
           <t>경량스터드</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>50 / 65 / 100 / 150형</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>LS 계열 · 불연 요구 현장</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="56" customHeight="1">
-      <c r="A51" s="9" t="inlineStr">
+    <row r="56"/>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
         <is>
           <t>실 단위 등급(AC-R) 우선: 실을 감싸는 6면 중 한 면이라도 등급이 낮으면 그 면이 실 성능을 결정함. 벽 4면을 L4로 시공해도 천장이 L1이면 천장으로 나감. 견적·도면에 실 등급을 먼저 표기하고 면별 구법을 그 아래 붙임. WS와 WP는 같은 등급이라도 두께가 다르므로(구조체 유무) 4면 마감선 불일치는 공틀 조정 또는 평면 계획에서 흡수.</t>
         </is>
       </c>
-      <c r="B51" s="10" t="n"/>
-      <c r="C51" s="10" t="n"/>
-      <c r="D51" s="10" t="n"/>
-    </row>
-    <row r="53" ht="56" customHeight="1">
-      <c r="A53" s="11" t="inlineStr">
+    </row>
+    <row r="58"/>
+    <row r="59">
+      <c r="A59" s="11" t="inlineStr">
         <is>
           <t>AC-A / AC-B 관계: 본 시트는 AC-A(직접 시공) 계열이며 L5가 상한. 지하철·기계실 인접 등 구조전달 진동 현장은 벽 두께로 해결되지 않으므로 AC-B(박스인박스)로 계열 전환. 착공 전 슬래브 진동 실측이 선행되어야 하며, 삼중 구성은 저역에서 오히려 악화되므로 어떤 등급에서도 채택하지 않음.</t>
         </is>
       </c>
-      <c r="B53" s="12" t="n"/>
-      <c r="C53" s="12" t="n"/>
-      <c r="D53" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1408,7 +1603,7 @@
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>이중 하지 칸막이 (분리 확대)</t>
+          <t>이중 벽체틀 (분리 확대)</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1726,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>이중 하지 칸막이 (분리 확대)</t>
+          <t>이중 벽체틀 (분리 확대)</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1745,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>하지 — LT (목재)</t>
+          <t>벽체틀 — LT (목재)</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -1562,7 +1757,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>하지 — LS (경량스터드)</t>
+          <t>벽체틀 — LS (경량스터드)</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -1603,7 +1798,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>미네랄울 48K 50T × 2</t>
+          <t>미네랄울 50K 50T × 2</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1834,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>상하부 런너 고무패드 3T · 사방 방음 실란트 · 미네랄울 48K · 슬래브 도달 필수 · 양면 대칭</t>
+          <t>상하부 런너 고무패드 3T · 사방 방음 실란트 · 미네랄울 50K · 슬래브 도달 필수 · 양면 대칭</t>
         </is>
       </c>
     </row>
@@ -1685,9 +1880,6 @@
           <t>L3 → L4는 분리 간격만 달라집니다. 성능 개선폭은 크지 않으나 열간 접촉 사고가 줄어드는 시공 여유가 실질적 가치입니다. 두께 제약이 있으면 L3(252mm)로도 충분하며, 여유가 있으면 L4를 표준으로 잡습니다.</t>
         </is>
       </c>
-      <c r="B29" s="12" t="n"/>
-      <c r="C29" s="12" t="n"/>
-      <c r="D29" s="12" t="n"/>
     </row>
     <row r="31" ht="56" customHeight="1">
       <c r="A31" s="9" t="inlineStr">
@@ -1695,9 +1887,6 @@
           <t>삼중 구성으로 늘리지 않습니다. 판을 3장으로 만들면 공기층이 둘로 쪼개져 저역에서 오히려 나빠집니다. 그 이상이 필요하면 AC-B(박스인박스)로 계열이 바뀝니다.</t>
         </is>
       </c>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
-      <c r="D31" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -1880,7 +2069,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>미네랄울 48K 50T × 2</t>
+          <t>미네랄울 50K 50T × 2</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -1929,9 +2118,6 @@
           <t>추정치 주의: f₀는 중공층 깊이와 면밀도로부터의 계산 추정값이며 실측 성적서가 아님. 내부 등급 비교 및 상담 설명 목적으로만 사용하고 대외 자료·견적서에 성능 수치로 기재하지 않음. 성능 보증이 필요한 현장은 시공 후 실측을 별도 항목으로 계상.</t>
         </is>
       </c>
-      <c r="B49" s="10" t="n"/>
-      <c r="C49" s="10" t="n"/>
-      <c r="D49" s="10" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -1973,7 +2159,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>목재 하지</t>
+          <t>목재 벽체틀</t>
         </is>
       </c>
     </row>
@@ -1997,17 +2183,17 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>미네랄울 보드</t>
+          <t>미네랄울 보온판 50K</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>48K · 50T × 2</t>
+          <t>50K · 50T · 450×1000 × 2</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>KCC 또는 벽산 · 라이트필 031-604-3000</t>
+          <t>벽산 또는 KCC · 라이트필 031-604-3000</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2290,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>판 두께 + 하지 물림</t>
+          <t>판 두께 + 벽체틀 물림</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -2576,7 +2762,7 @@
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>이중 하지 칸막이 (질량 보강)</t>
+          <t>이중 벽체틀 (질량 보강)</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2885,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>이중 하지 칸막이 (질량 보강)</t>
+          <t>이중 벽체틀 (질량 보강)</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2904,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>하지 — LT (목재)</t>
+          <t>벽체틀 — LT (목재)</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -2730,7 +2916,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>하지 — LS (경량스터드)</t>
+          <t>벽체틀 — LS (경량스터드)</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -2771,7 +2957,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>미네랄울 48K 50T × 2</t>
+          <t>미네랄울 50K 50T × 2</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2993,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>상하부 런너 고무패드 3T · 사방 방음 실란트 · 미네랄울 48K · 슬래브 도달 필수 · 양면 대칭</t>
+          <t>상하부 런너 고무패드 3T · 사방 방음 실란트 · 미네랄울 50K · 슬래브 도달 필수 · 양면 대칭</t>
         </is>
       </c>
     </row>
@@ -2853,9 +3039,6 @@
           <t>L5는 AC-A(직접 시공)의 상한입니다. 분리 50mm, 충진 100T, 판 보강까지 모두 사용한 구성이며 그 이상은 두께로 해결되지 않습니다. 더 필요하면 AC-B(박스인박스)로 계열이 바뀝니다.</t>
         </is>
       </c>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="10" t="n"/>
-      <c r="D29" s="10" t="n"/>
     </row>
     <row r="31" ht="56" customHeight="1">
       <c r="A31" s="17" t="inlineStr">
@@ -2863,9 +3046,6 @@
           <t>6면 등급 일치가 전제입니다. 칸막이 양면을 L5로 해도 바닥·천장이 낮으면 그쪽으로 나갑니다. 실 단위 등급(AC-R)으로 관리하며, F·C 시리즈가 동급 이상으로 따라와야 실효 성능이 나옵니다.</t>
         </is>
       </c>
-      <c r="B31" s="18" t="n"/>
-      <c r="C31" s="18" t="n"/>
-      <c r="D31" s="18" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -3065,7 +3245,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>미네랄울 48K 50T × 2</t>
+          <t>미네랄울 50K 50T × 2</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -3114,9 +3294,6 @@
           <t>추정치 주의: f₀는 중공층 깊이와 면밀도로부터의 계산 추정값이며 실측 성적서가 아님. 내부 등급 비교 및 상담 설명 목적으로만 사용하고 대외 자료·견적서에 성능 수치로 기재하지 않음. 성능 보증이 필요한 현장은 시공 후 실측을 별도 항목으로 계상.</t>
         </is>
       </c>
-      <c r="B50" s="10" t="n"/>
-      <c r="C50" s="10" t="n"/>
-      <c r="D50" s="10" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -3158,7 +3335,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>목재 하지</t>
+          <t>목재 벽체틀</t>
         </is>
       </c>
     </row>
@@ -3182,17 +3359,17 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>미네랄울 보드</t>
+          <t>미네랄울 보온판 50K</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>48K · 50T × 2</t>
+          <t>50K · 50T · 450×1000 × 2</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>KCC 또는 벽산 · 라이트필 031-604-3000</t>
+          <t>벽산 또는 KCC · 라이트필 031-604-3000</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3483,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>판 두께 + 하지 물림</t>
+          <t>판 두께 + 벽체틀 물림</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -3729,6 +3906,3032 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D85"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>AC-W-M1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>유닛 조립형 벽체 · 내부벽</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="26" t="inlineStr">
+        <is>
+          <t>Prefab unit wall / interior partition</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>메타</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="n"/>
+      <c r="C5" s="15" t="n"/>
+      <c r="D5" s="15" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>부위</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>벽 Wall — 유닛 조립형</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>등급</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>총 두께</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>145 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>분류</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>흡음 + 차음</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>아파트 · 오피스텔</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>개정</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>사양</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="n"/>
+      <c r="C13" s="15" t="n"/>
+      <c r="D13" s="15" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>명칭</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>유닛 조립형 벽체 · 내부벽</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>구성</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>기존 내부벽 + PB 15T 보강 + 마블 50T + PB 15T + PB 15T + 마블 50T</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t>유닛</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>600×1200 · PB 15T + 프레임 + 마블 중마 70K 50T · 2겹</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="28" t="inlineStr">
+        <is>
+          <t>중공층</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>마블 50T × 2 = 100mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="28" t="inlineStr">
+        <is>
+          <t>지지</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>상 · 하부 런너 고무패드 3T · 벽면 비고정</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>체결</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>전 부재 피스 · 접착제 사용 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="28" t="inlineStr">
+        <is>
+          <t>마감</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>지정 마감 (별도 사양) — AC-AB 참조</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="28" t="inlineStr">
+        <is>
+          <t>적용</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>같은 세대 내부와 맞닿은 벽</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="30" t="inlineStr">
+        <is>
+          <t>비대응</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>어쿠스틱 드럼 · 베이스앰프 · 서브우퍼</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>유닛 B를 뒤집어 PB끼리 맞댄다. 두 PB가 한 덩어리로 거동하여 20.4 kg/㎡ 판이 되고, 실내측 마블이 그대로 흡음 배후층이 된다.</t>
+        </is>
+      </c>
+      <c r="B24" s="32" t="n"/>
+      <c r="C24" s="32" t="n"/>
+      <c r="D24" s="32" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="27" t="inlineStr">
+        <is>
+          <t>면밀도 배분</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="n"/>
+      <c r="C26" s="15" t="n"/>
+      <c r="D26" s="15" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="33" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B27" s="33" t="inlineStr">
+        <is>
+          <t>개략 면밀도</t>
+        </is>
+      </c>
+      <c r="C27" s="33" t="inlineStr">
+        <is>
+          <t>위치</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>기존 벽 + 보강 PB</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>25.2 kg/㎡</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>벽쪽</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>PB 15T × 2 맞댐</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>20.4 kg/㎡</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>실내측</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="52" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>가벼운 판을 먼저 잡는다. M-S-M 시스템은 두 판의 면밀도가 균형에 가까울수록 공진주파수가 낮아진다. 같은 자재 한 장이라도 무거운 쪽보다 가벼운 쪽에 붙이는 것이 효율이 높다. 경계벽이 콘크리트면 이미 460이므로 실내측에, 건식이면 19이므로 기존 벽면에 먼저 투입한다.</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="n"/>
+      <c r="C31" s="12" t="n"/>
+      <c r="D31" s="12" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="27" t="inlineStr">
+        <is>
+          <t>유닛 사양</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="n"/>
+      <c r="C33" s="15" t="n"/>
+      <c r="D33" s="15" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="28" t="inlineStr">
+        <is>
+          <t>규격</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>600 × 1200mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="28" t="inlineStr">
+        <is>
+          <t>구성</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>PB 15T + 프레임 + 마블 중마 70K 50T</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="28" t="inlineStr">
+        <is>
+          <t>두께</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>65mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="28" t="inlineStr">
+        <is>
+          <t>중량</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>약 11 kg/장 — 1인 운반</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="28" t="inlineStr">
+        <is>
+          <t>제작</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>작업장 선제작 · 현장 조립</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="28" t="inlineStr">
+        <is>
+          <t>체결</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>전 부재 피스 — 접착제 사용 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="28" t="inlineStr">
+        <is>
+          <t>해체</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>가능 — 회수 후 타 현장 재사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="30" t="inlineStr">
+        <is>
+          <t>프레임 재료</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>확인 필요 — 다루끼 + 합판 / PB</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="30" t="inlineStr">
+        <is>
+          <t>상부 턱</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>확인 필요 — 유닛 포함 / 현장 시공</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="52" customHeight="1">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>PB 원판 1220×2440을 4등분한 치수다. 로스가 거의 없고 1인 운반이 가능해 엘리베이터·계단 반입에 제약이 없다. 재사용이 이 공법의 핵심이므로 접착제를 쓰지 않고 전 부재를 피스로 체결하며, 유닛 뒷면에 실명과 위치를 표기한다. 차음석고·마감재는 소모품이므로 견적에서 유닛(자산)과 분리해 계상한다.</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="n"/>
+      <c r="C44" s="12" t="n"/>
+      <c r="D44" s="12" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="27" t="inlineStr">
+        <is>
+          <t>자재</t>
+        </is>
+      </c>
+      <c r="B46" s="15" t="n"/>
+      <c r="C46" s="15" t="n"/>
+      <c r="D46" s="15" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="33" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B47" s="33" t="inlineStr">
+        <is>
+          <t>규격</t>
+        </is>
+      </c>
+      <c r="C47" s="33" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>유닛</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>600×1200 · PB 15T + 프레임 + 마블 50T</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>2겹 · 회수 재사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>PB (보강)</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>15T</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>벽면 직접 · 접착 + 상하부 고정</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>마블 중마</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>70K · 50T</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>유닛 내장</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>고무패드</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>3T</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>상하부 런너</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>피스</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>25mm 이하</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>유닛 관통 길이 반입 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>탄성 실란트</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>단부 · 관통부</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>지정 마감</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>타공 흡음판 · 목모보드</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>별도 사양 — AC-AB 참조</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="27" t="inlineStr">
+        <is>
+          <t>시공 순서</t>
+        </is>
+      </c>
+      <c r="B56" s="15" t="n"/>
+      <c r="C56" s="15" t="n"/>
+      <c r="D56" s="15" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B57" s="33" t="inlineStr">
+        <is>
+          <t>작업</t>
+        </is>
+      </c>
+      <c r="C57" s="33" t="inlineStr">
+        <is>
+          <t>확인사항</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>기존 벽면 정리</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>돌출부 · 이물 제거</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>벽면 PB 15T 보강</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>접착 + 상하부 고정 · 벽 관통 피스 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>하부 런너</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>고무패드 3T 개재 · 먹줄 확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>유닛 A 설치</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>마블면이 벽을 향함 · 반 칸 어긋내기</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>유닛 B 설치</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>뒤집어 PB끼리 맞댐 · 방향 표시 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>유닛 간 체결</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>프레임에서 프레임 · 마블 관통 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>상부 턱 · 런너</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>천장 보 지지부 · 수평 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>단부 실란트</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>사방 전 둘레</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>지정 마감</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>별도 사양</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="27" t="inlineStr">
+        <is>
+          <t>시공상 유의사항</t>
+        </is>
+      </c>
+      <c r="B68" s="15" t="n"/>
+      <c r="C68" s="15" t="n"/>
+      <c r="D68" s="15" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="33" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B69" s="33" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>유닛 방향 표시</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>유닛 B만 뒤집는다. 작업장에서 뒷면에 방향 표시를 해두면 현장에서 틀리지 않는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>반 칸 어긋내기</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>두 유닛의 프레임이 마주보면 그 선이 관통 경로가 된다. 반 칸 밀어 배치하면 프레임 뒤에 마블이 온다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>벽면 피스 금지</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>보강 PB는 접착과 상하부 고정으로만 잡는다. 벽에 피스를 박으면 진동이 넘어오고 원상복구가 안 된다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>유닛 관통 피스 금지</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>유닛끼리 연결할 때 마블을 관통하면 두 판이 직결된다. 피스는 25mm 이하만 반입한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>마블 압착 금지</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>유닛을 밀착시킬 때 마블이 눌리면 흐름저항이 저하되고 재료가 두 판을 잇는 경로가 된다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>콘센트 박스</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>유닛을 관통하는 매입 박스는 그 지점만 벽이 없는 것과 같다. 표면 배선 또는 방진 백박스로 처리한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>회수 관리</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>유닛 뒷면에 실명과 위치를 표기한다. 실 치수에 맞춰 재단된 유닛이 섞이면 재조립이 안 된다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="27" t="inlineStr">
+        <is>
+          <t>금지사항</t>
+        </is>
+      </c>
+      <c r="B78" s="15" t="n"/>
+      <c r="C78" s="15" t="n"/>
+      <c r="D78" s="15" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="33" t="inlineStr">
+        <is>
+          <t>금지</t>
+        </is>
+      </c>
+      <c r="B79" s="33" t="inlineStr">
+        <is>
+          <t>사유</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>벽면에 피스 고정</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>진동 직결 · 원상복구 불가</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>유닛 관통 피스</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>두 판 직결 — 중공층 무효</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>유닛 프레임 정렬 배치</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>관통 경로 형성 — 반 칸 어긋내기</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>마블 압착 시공</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>흐름저항 저하 · 브릿지</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>상하부 고무패드 생략</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>유일한 전달 경로 개방</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>추정 성능 대외 기재</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>마블 흡음 데이터 미확보</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A44:D44"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D89"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>AC-W-M2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>유닛 조립형 벽체 · 콘크리트 경계벽</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="26" t="inlineStr">
+        <is>
+          <t>Prefab unit wall / concrete party wall</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>메타</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="n"/>
+      <c r="C5" s="15" t="n"/>
+      <c r="D5" s="15" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>부위</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>벽 Wall — 유닛 조립형</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>등급</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>총 두께</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>143 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>분류</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>차음</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>아파트 · 오피스텔</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>개정</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>사양</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="n"/>
+      <c r="C13" s="15" t="n"/>
+      <c r="D13" s="15" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>명칭</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>유닛 조립형 벽체 · 콘크리트 경계벽</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>구성</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>콘크리트 경계벽 + 마블 50T + PB 15T + 마블 50T + PB 15T + 돌차음판 4T + 차음석고 12.5T</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t>유닛</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>600×1200 · PB 15T + 프레임 + 마블 중마 70K 50T · 2겹</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="28" t="inlineStr">
+        <is>
+          <t>중공층</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>마블 50T × 2 = 100mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="28" t="inlineStr">
+        <is>
+          <t>지지</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>상 · 하부 런너 고무패드 3T · 벽면 비고정</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>체결</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>전 부재 피스 · 접착제 사용 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="28" t="inlineStr">
+        <is>
+          <t>마감</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>지정 마감 (별도 사양) — AC-AB 참조</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="28" t="inlineStr">
+        <is>
+          <t>적용</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>타세대와 맞닿은 콘크리트 경계벽</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="30" t="inlineStr">
+        <is>
+          <t>비대응</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>어쿠스틱 드럼 · 베이스앰프 · 서브우퍼</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>유닛 두 겹을 같은 방향으로 세운다. 마블면이 벽을 향해 이격재 역할을 하고, 실내측 PB 위에 차음석고를 현장에서 시공한다.</t>
+        </is>
+      </c>
+      <c r="B24" s="32" t="n"/>
+      <c r="C24" s="32" t="n"/>
+      <c r="D24" s="32" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="27" t="inlineStr">
+        <is>
+          <t>면밀도 배분</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="n"/>
+      <c r="C26" s="15" t="n"/>
+      <c r="D26" s="15" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="33" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B27" s="33" t="inlineStr">
+        <is>
+          <t>개략 면밀도</t>
+        </is>
+      </c>
+      <c r="C27" s="33" t="inlineStr">
+        <is>
+          <t>위치</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>콘크리트 경계벽</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>약 460 kg/㎡</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>고정단에 가까움</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>PB 15T (유닛 A)</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>10.2 kg/㎡</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>PB 15 + 차음석고 12.5</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>23.2 kg/㎡</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>실내측 · 옵션 시 30.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="52" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>가벼운 판을 먼저 잡는다. M-S-M 시스템은 두 판의 면밀도가 균형에 가까울수록 공진주파수가 낮아진다. 같은 자재 한 장이라도 무거운 쪽보다 가벼운 쪽에 붙이는 것이 효율이 높다. 경계벽이 콘크리트면 이미 460이므로 실내측에, 건식이면 19이므로 기존 벽면에 먼저 투입한다.</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="12" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="27" t="inlineStr">
+        <is>
+          <t>유닛 사양</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="n"/>
+      <c r="C34" s="15" t="n"/>
+      <c r="D34" s="15" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="28" t="inlineStr">
+        <is>
+          <t>규격</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>600 × 1200mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="28" t="inlineStr">
+        <is>
+          <t>구성</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>PB 15T + 프레임 + 마블 중마 70K 50T</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="28" t="inlineStr">
+        <is>
+          <t>두께</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>65mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="28" t="inlineStr">
+        <is>
+          <t>중량</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>약 11 kg/장 — 1인 운반</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="28" t="inlineStr">
+        <is>
+          <t>제작</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>작업장 선제작 · 현장 조립</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="28" t="inlineStr">
+        <is>
+          <t>체결</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>전 부재 피스 — 접착제 사용 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="28" t="inlineStr">
+        <is>
+          <t>해체</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>가능 — 회수 후 타 현장 재사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="30" t="inlineStr">
+        <is>
+          <t>프레임 재료</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>확인 필요 — 다루끼 + 합판 / PB</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="30" t="inlineStr">
+        <is>
+          <t>상부 턱</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>확인 필요 — 유닛 포함 / 현장 시공</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="52" customHeight="1">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>PB 원판 1220×2440을 4등분한 치수다. 로스가 거의 없고 1인 운반이 가능해 엘리베이터·계단 반입에 제약이 없다. 재사용이 이 공법의 핵심이므로 접착제를 쓰지 않고 전 부재를 피스로 체결하며, 유닛 뒷면에 실명과 위치를 표기한다. 차음석고·마감재는 소모품이므로 견적에서 유닛(자산)과 분리해 계상한다.</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="n"/>
+      <c r="C45" s="12" t="n"/>
+      <c r="D45" s="12" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="27" t="inlineStr">
+        <is>
+          <t>자재</t>
+        </is>
+      </c>
+      <c r="B47" s="15" t="n"/>
+      <c r="C47" s="15" t="n"/>
+      <c r="D47" s="15" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="33" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B48" s="33" t="inlineStr">
+        <is>
+          <t>규격</t>
+        </is>
+      </c>
+      <c r="C48" s="33" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>유닛</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>600×1200 · PB 15T + 프레임 + 마블 50T</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>2겹 · 회수 재사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>마블 중마</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>70K · 50T</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>유닛 내장</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>차음석고보드</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>12.5T</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>현장 시공 · 이음 600 엇갈림</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>돌차음판</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>4T · 자체 점착</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>선택 사양 · 실내측</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>고무패드</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>3T</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>상하부 런너</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>피스</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>25mm 이하</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>유닛 관통 길이 반입 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>탄성 실란트</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>단부 · 관통부</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>지정 마감</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>별도 사양 — AC-AB 참조</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="27" t="inlineStr">
+        <is>
+          <t>시공 순서</t>
+        </is>
+      </c>
+      <c r="B58" s="15" t="n"/>
+      <c r="C58" s="15" t="n"/>
+      <c r="D58" s="15" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B59" s="33" t="inlineStr">
+        <is>
+          <t>작업</t>
+        </is>
+      </c>
+      <c r="C59" s="33" t="inlineStr">
+        <is>
+          <t>확인사항</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>경계벽 면 정리</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>돌출부 · 이물 제거</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>하부 런너</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>고무패드 3T 개재 · 먹줄 확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>유닛 A 설치</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>마블면이 벽을 향함</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>유닛 B 설치</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>동일 방향 · 반 칸 어긋내기</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>유닛 간 체결</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>프레임에서 프레임 · 마블 관통 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>상부 턱 · 런너</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>천장 보 지지부 · 수평 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>돌차음판 4T</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>선택 사양 · 이형지 20~30cm씩</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>차음석고 12.5T</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>프레임 위치 피스 · 이음 600 엇갈림</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>단부 실란트</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>사방 전 둘레</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>지정 마감</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>별도 사양</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="27" t="inlineStr">
+        <is>
+          <t>시공상 유의사항</t>
+        </is>
+      </c>
+      <c r="B71" s="15" t="n"/>
+      <c r="C71" s="15" t="n"/>
+      <c r="D71" s="15" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="33" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B72" s="33" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>마감판은 현장 시공</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>유닛에 미리 붙이면 600마다 관통 이음선이 생긴다. 현장에서 쳐야 유닛 경계를 가로질러 덮인다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>프레임 위치 먹줄</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>차음석고 피스는 유닛 프레임에만 물린다. 작업장에서 유닛 표면에 프레임 위치를 그어두면 현장에서 헤매지 않는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>본드 병용 금지</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>재사용을 전제하므로 유닛 표면에 접착제를 쓰지 않는다. 떼면 PB 표면이 뜯긴다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>반 칸 어긋내기</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>두 유닛의 프레임이 마주보면 관통 경로가 된다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>유닛 관통 피스 금지</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>피스는 25mm 이하만 반입한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>콘센트 박스</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>유닛 관통 매입 금지. 표면 배선 또는 방진 백박스.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>회수 관리</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>유닛 뒷면에 실명과 위치 표기. 차음석고는 소모품으로 별도 계상한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="27" t="inlineStr">
+        <is>
+          <t>금지사항</t>
+        </is>
+      </c>
+      <c r="B81" s="15" t="n"/>
+      <c r="C81" s="15" t="n"/>
+      <c r="D81" s="15" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="33" t="inlineStr">
+        <is>
+          <t>금지</t>
+        </is>
+      </c>
+      <c r="B82" s="33" t="inlineStr">
+        <is>
+          <t>사유</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>마감판을 유닛에 선부착</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>600마다 관통 이음선 형성</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>유닛 표면 접착제 사용</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>재사용 불가 — 피스 체결만</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>유닛 관통 피스</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>두 판 직결</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>유닛 프레임 정렬 배치</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>관통 경로 형성</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>경계벽에 피스 고정</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>구조전달 · 원상복구 불가</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>드럼 · 서브우퍼 현장 적용</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>아파트 구조에서 대응 불가</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>추정 성능 대외 기재</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>마블 흡음 데이터 미확보</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A24:D24"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D90"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>AC-W-M3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>유닛 조립형 벽체 · 건식 경계벽</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="26" t="inlineStr">
+        <is>
+          <t>Prefab unit wall / drywall party wall</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>메타</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="n"/>
+      <c r="C5" s="15" t="n"/>
+      <c r="D5" s="15" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>부위</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>벽 Wall — 유닛 조립형</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>등급</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>총 두께</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>155 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>분류</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>차음 (기존 벽 보강)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>아파트 · 오피스텔</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>개정</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>사양</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="n"/>
+      <c r="C13" s="15" t="n"/>
+      <c r="D13" s="15" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>명칭</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>유닛 조립형 벽체 · 건식 경계벽</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>구성</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>건식 경계벽 + 차음석고 12.5T + 마블 50T + PB 15T + 마블 50T + PB 15T + 돌차음판 4T + 차음석고 12.5T</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t>유닛</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>600×1200 · PB 15T + 프레임 + 마블 중마 70K 50T · 2겹</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="28" t="inlineStr">
+        <is>
+          <t>중공층</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>마블 50T × 2 = 100mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="28" t="inlineStr">
+        <is>
+          <t>지지</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>상 · 하부 런너 고무패드 3T · 벽면 비고정</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>체결</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>전 부재 피스 · 접착제 사용 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="28" t="inlineStr">
+        <is>
+          <t>마감</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>지정 마감 (별도 사양) — AC-AB 참조</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="28" t="inlineStr">
+        <is>
+          <t>적용</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>주상복합 등 건식 경계벽 (스터드 + 석고)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="30" t="inlineStr">
+        <is>
+          <t>비대응</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>어쿠스틱 드럼 · 베이스앰프 · 서브우퍼</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>M2와 구성은 같고 기존 벽면에 차음석고 한 겹을 더한다. 가장 가벼운 판을 먼저 잡는 것이 원칙이다.</t>
+        </is>
+      </c>
+      <c r="B24" s="32" t="n"/>
+      <c r="C24" s="32" t="n"/>
+      <c r="D24" s="32" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="27" t="inlineStr">
+        <is>
+          <t>면밀도 배분</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="n"/>
+      <c r="C26" s="15" t="n"/>
+      <c r="D26" s="15" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="33" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B27" s="33" t="inlineStr">
+        <is>
+          <t>개략 면밀도</t>
+        </is>
+      </c>
+      <c r="C27" s="33" t="inlineStr">
+        <is>
+          <t>위치</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>건식 경계벽 + 보강 석고</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>약 32 kg/㎡</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>19 → 32 · 68% 증가</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>PB 15T (유닛 A)</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>10.2 kg/㎡</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>PB 15 + 차음석고 12.5</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>23.2 kg/㎡</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>실내측 · 옵션 시 30.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="52" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>가벼운 판을 먼저 잡는다. M-S-M 시스템은 두 판의 면밀도가 균형에 가까울수록 공진주파수가 낮아진다. 같은 자재 한 장이라도 무거운 쪽보다 가벼운 쪽에 붙이는 것이 효율이 높다. 경계벽이 콘크리트면 이미 460이므로 실내측에, 건식이면 19이므로 기존 벽면에 먼저 투입한다.</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="12" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="27" t="inlineStr">
+        <is>
+          <t>유닛 사양</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="n"/>
+      <c r="C34" s="15" t="n"/>
+      <c r="D34" s="15" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="28" t="inlineStr">
+        <is>
+          <t>규격</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>600 × 1200mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="28" t="inlineStr">
+        <is>
+          <t>구성</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>PB 15T + 프레임 + 마블 중마 70K 50T</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="28" t="inlineStr">
+        <is>
+          <t>두께</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>65mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="28" t="inlineStr">
+        <is>
+          <t>중량</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>약 11 kg/장 — 1인 운반</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="28" t="inlineStr">
+        <is>
+          <t>제작</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>작업장 선제작 · 현장 조립</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="28" t="inlineStr">
+        <is>
+          <t>체결</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>전 부재 피스 — 접착제 사용 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="28" t="inlineStr">
+        <is>
+          <t>해체</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>가능 — 회수 후 타 현장 재사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="30" t="inlineStr">
+        <is>
+          <t>프레임 재료</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>확인 필요 — 다루끼 + 합판 / PB</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="30" t="inlineStr">
+        <is>
+          <t>상부 턱</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>확인 필요 — 유닛 포함 / 현장 시공</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="52" customHeight="1">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>PB 원판 1220×2440을 4등분한 치수다. 로스가 거의 없고 1인 운반이 가능해 엘리베이터·계단 반입에 제약이 없다. 재사용이 이 공법의 핵심이므로 접착제를 쓰지 않고 전 부재를 피스로 체결하며, 유닛 뒷면에 실명과 위치를 표기한다. 차음석고·마감재는 소모품이므로 견적에서 유닛(자산)과 분리해 계상한다.</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="n"/>
+      <c r="C45" s="12" t="n"/>
+      <c r="D45" s="12" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="27" t="inlineStr">
+        <is>
+          <t>자재</t>
+        </is>
+      </c>
+      <c r="B47" s="15" t="n"/>
+      <c r="C47" s="15" t="n"/>
+      <c r="D47" s="15" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="33" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B48" s="33" t="inlineStr">
+        <is>
+          <t>규격</t>
+        </is>
+      </c>
+      <c r="C48" s="33" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>차음석고보드</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>12.5T</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>기존 벽면 + 실내측 · 2개소</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>유닛</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>600×1200 · PB 15T + 프레임 + 마블 50T</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>2겹 · 회수 재사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>마블 중마</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>70K · 50T</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>유닛 내장</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>돌차음판</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>4T · 자체 점착</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>선택 사양 · 벽면 우선</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>고무패드</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>3T</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>상하부 런너</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>피스</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>25mm 이하</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>유닛 관통 길이 반입 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>탄성 실란트</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>단부 · 관통부</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>지정 마감</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>별도 사양 — AC-AB 참조</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="27" t="inlineStr">
+        <is>
+          <t>시공 순서</t>
+        </is>
+      </c>
+      <c r="B58" s="15" t="n"/>
+      <c r="C58" s="15" t="n"/>
+      <c r="D58" s="15" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B59" s="33" t="inlineStr">
+        <is>
+          <t>작업</t>
+        </is>
+      </c>
+      <c r="C59" s="33" t="inlineStr">
+        <is>
+          <t>확인사항</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>경계벽 콘센트 점검</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>양면 마주보기 여부 확인 · 방진 백박스 교체</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>기존 벽면 보강</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>차음석고 12.5T · 접착 + 상하부 고정</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>하부 런너</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>고무패드 3T 개재 · 먹줄 확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>유닛 A 설치</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>마블면이 벽을 향함</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>유닛 B 설치</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>동일 방향 · 반 칸 어긋내기</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>유닛 간 체결</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>프레임에서 프레임 · 마블 관통 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>상부 턱 · 런너</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>천장 보 지지부 · 수평 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>돌차음판 4T</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>선택 사양</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>차음석고 12.5T</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>프레임 위치 피스 · 이음 600 엇갈림</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>단부 실란트</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>사방 전 둘레</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>지정 마감</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>별도 사양</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="27" t="inlineStr">
+        <is>
+          <t>시공상 유의사항</t>
+        </is>
+      </c>
+      <c r="B72" s="15" t="n"/>
+      <c r="C72" s="15" t="n"/>
+      <c r="D72" s="15" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="33" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B73" s="33" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>벽면 피스 절대 금지</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>석고에 박히면 유지력이 없고, 스터드에 박히면 옆세대까지 직결된다. 접착과 상하부 고정으로만 잡는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>콘센트 선행 점검</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>건식 경계벽은 양면 콘센트가 마주보게 시공된 경우가 많다. 그 지점은 벽이 뚫린 것과 같아 착공 전 밀봉하거나 방진 백박스로 교체한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>경계벽 철거 금지</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>세대 간 경계벽은 내화구조이자 법정 차음 구조다. 임의로 손댈 수 없으며 덧대는 것만 가능하다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>돌차음판은 벽면 우선</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>옵션을 하나만 적용한다면 실내측이 아니라 기존 벽면 쪽이다. 가벼운 판을 먼저 잡는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>마감판은 현장 시공</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>유닛 경계를 가로질러 덮어야 이음이 엇갈린다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>반 칸 어긋내기</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>두 유닛의 프레임이 마주보면 관통 경로가 된다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>성능 한계 고지</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>기존 벽이 이미 이중 시스템이라 리프가 넷 이상이다. 저역은 콘크리트 현장만큼 나오지 않는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="27" t="inlineStr">
+        <is>
+          <t>금지사항</t>
+        </is>
+      </c>
+      <c r="B82" s="15" t="n"/>
+      <c r="C82" s="15" t="n"/>
+      <c r="D82" s="15" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="33" t="inlineStr">
+        <is>
+          <t>금지</t>
+        </is>
+      </c>
+      <c r="B83" s="33" t="inlineStr">
+        <is>
+          <t>사유</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>경계벽에 피스 고정</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>스터드 관통 시 옆세대 직결</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>경계벽 철거 · 개조</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>내화구조 · 법정 차음 구조</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>콘센트 미점검 착공</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>마주보기 지점이 개구부로 남음</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>벽면 보강 생략</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>가장 약한 고리 방치</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>유닛 관통 피스</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>두 판 직결</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>저역 음원 현장 적용</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>앰프 · 드럼 · 서브우퍼 대응 불가</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>추정 성능 대외 기재</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>마블 흡음 데이터 미확보</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A24:D24"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3888,7 +7091,7 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>하지 축 (벽 · 천장 공통)</t>
+          <t>벽체틀 축 (벽 · 천장 공통)</t>
         </is>
       </c>
       <c r="B17" s="15" t="n"/>
@@ -3903,7 +7106,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>목재 하지 Timber — 투바이 각재. 하중 지지 · 이중벽 정밀도 유리</t>
+          <t>목재 벽체틀 Timber — 투바이 각재. 하중 지지 · 이중벽 정밀도 유리</t>
         </is>
       </c>
     </row>
@@ -3934,12 +7137,9 @@
     <row r="22" ht="56" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>LS를 써야 하는 현장: 방화구획 관통·접촉 벽체 / 내화구조 요구부 / 다중이용업소·학원·어린이집 등 불연 요구 / 지하층·무창층 / 습기·결로 우려 구간 / 감리가 목재 하지를 반려하는 경우. 실무상 마지막 항목이 가장 빈번하므로 착공 전 감리 확인 권장.</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="n"/>
-      <c r="C22" s="12" t="n"/>
-      <c r="D22" s="12" t="n"/>
+          <t>LS를 써야 하는 현장: 방화구획 관통·접촉 벽체 / 내화구조 요구부 / 다중이용업소·학원·어린이집 등 불연 요구 / 지하층·무창층 / 습기·결로 우려 구간 / 감리가 목재 벽체틀을 반려하는 경우. 실무상 마지막 항목이 가장 빈번하므로 착공 전 감리 확인 권장.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -3959,7 +7159,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>AC-{부위}-{하지}-{등급}</t>
+          <t>AC-{부위}-{벽체틀}-{등급}</t>
         </is>
       </c>
     </row>
@@ -4267,14 +7467,14 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>돌차음판 4T + 각재 30×30(미네랄울 30T) + 일반석고 9.5T + 차음석고 12.5T</t>
+          <t>돌차음판 4T + 각재 30×30(PET 25T 45K) + 일반석고 9.5T + 차음석고 12.5T</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>하지 — LT (목재)</t>
+          <t>벽체틀 — LT (목재)</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -4286,7 +7486,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>하지 — LS (경량스터드)</t>
+          <t>벽체틀 — LS (경량스터드)</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -4327,7 +7527,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>미네랄울 48K 30T</t>
+          <t>PET 폴리에스터 25T 45K</t>
         </is>
       </c>
     </row>
@@ -4363,7 +7563,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>돌차음판 4T 자착(구조체 면) · 상하부 런너 고무패드 3T · 사방 방음 실란트 · 미네랄울 48K</t>
+          <t>돌차음판 4T 자착(구조체 면) · 상하부 런너 고무패드 3T · 사방 방음 실란트</t>
         </is>
       </c>
     </row>
@@ -4409,9 +7609,6 @@
           <t>L1은 이격이 없는 최하 등급입니다. 각재가 구조체에 직결되어 면접촉 전달이 그대로 남습니다. 고무패드는 감쇠일 뿐 차단이 아닙니다. 차음이 성립하는 최소선은 L2이며, L1은 두께 제약이 확실한 현장의 대안으로만 제안합니다.</t>
         </is>
       </c>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="10" t="n"/>
-      <c r="D29" s="10" t="n"/>
     </row>
     <row r="31" ht="56" customHeight="1">
       <c r="A31" s="17" t="inlineStr">
@@ -4419,9 +7616,6 @@
           <t>그린글루는 L3부터. L1·L2는 구조 전달이 지배적인 구간이라 제진재를 넣어도 그 경로로 새나갑니다. 같은 예산이면 중공층 확보가 우선입니다.</t>
         </is>
       </c>
-      <c r="B31" s="18" t="n"/>
-      <c r="C31" s="18" t="n"/>
-      <c r="D31" s="18" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -4570,7 +7764,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>미네랄울 48K 30T</t>
+          <t>PET 폴리에스터 25T 45K</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -4619,9 +7813,6 @@
           <t>추정치 주의: f₀는 중공층 깊이와 면밀도로부터의 계산 추정값이며 실측 성적서가 아님. 내부 등급 비교 및 상담 설명 목적으로만 사용하고 대외 자료·견적서에 성능 수치로 기재하지 않음. 성능 보증이 필요한 현장은 시공 후 실측을 별도 항목으로 계상.</t>
         </is>
       </c>
-      <c r="B47" s="10" t="n"/>
-      <c r="C47" s="10" t="n"/>
-      <c r="D47" s="10" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -4680,7 +7871,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>목재 하지</t>
+          <t>목재 벽체틀</t>
         </is>
       </c>
     </row>
@@ -4704,17 +7895,17 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>미네랄울 보드</t>
+          <t>PET 폴리에스터 흡음단열재</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>48K · 30T</t>
+          <t>45K · 25T · 1000×2000</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>KCC 또는 벽산 · 라이트필 031-604-3000</t>
+          <t>N25폴리 45K · KS F 5660 — 미네랄울은 최소 50T로 30mm 중공층 적용 불가</t>
         </is>
       </c>
     </row>
@@ -4794,7 +7985,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>판 두께 + 하지 물림</t>
+          <t>판 두께 + 벽체틀 물림</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -4926,12 +8117,12 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>미네랄울 30T 충진</t>
+          <t>PET 25T 45K 충진</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>압축 금지 · 각재 사이 밀착만</t>
+          <t>각재 사이 밀착 · 압축 금지</t>
         </is>
       </c>
     </row>
@@ -5044,12 +8235,12 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>미네랄울 압축 금지</t>
+          <t>충진재 규격</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>30T를 그대로 유지. 눌러 넣으면 흐름저항 저하 + 판 접촉</t>
+          <t>중공층 30mm에는 미네랄울 적용 불가. 국내 유통 최소 두께가 50T이므로 물리적으로 들어가지 않음. PET 폴리에스터 25T 45K(KS F 5660)로 대체하며, 25T는 30mm 공간에 5mm 여유가 남아 압착이 발생하지 않음</t>
         </is>
       </c>
     </row>
@@ -5126,7 +8317,7 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>미네랄울 생략</t>
+          <t>충진재 생략</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
@@ -5348,7 +8539,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>하지 — LT (목재)</t>
+          <t>벽체틀 — LT (목재)</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -5360,7 +8551,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>하지 — LS (경량스터드)</t>
+          <t>벽체틀 — LS (경량스터드)</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -5401,7 +8592,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>미네랄울 48K 50T</t>
+          <t>미네랄울 50K 50T</t>
         </is>
       </c>
     </row>
@@ -5437,7 +8628,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>돌차음판 4T 자착(구조체 면) · 상하부 런너 고무패드 3T · 사방 방음 실란트 · 미네랄울 48K</t>
+          <t>돌차음판 4T 자착(구조체 면) · 상하부 런너 고무패드 3T · 사방 방음 실란트 · 미네랄울 50K</t>
         </is>
       </c>
     </row>
@@ -5483,9 +8674,6 @@
           <t>WS 주력 등급입니다. 중공층 67mm로 차음이 성립하는 최소선이면서 두께 93mm로 실 면적 손실이 크지 않습니다. 세대간벽·복도벽·일반 학원 실간벽의 표준 사양으로 제안합니다.</t>
         </is>
       </c>
-      <c r="B29" s="18" t="n"/>
-      <c r="C29" s="18" t="n"/>
-      <c r="D29" s="18" t="n"/>
     </row>
     <row r="31" ht="56" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
@@ -5493,9 +8681,6 @@
           <t>여기까지는 구조체 직결입니다. 각재가 돌차음판 면에 접해 있어 면접촉 전달이 남습니다. 이 경로를 끊는 것이 L3(이격형)이며, 저역 개선은 그 지점부터 시작됩니다.</t>
         </is>
       </c>
-      <c r="B31" s="12" t="n"/>
-      <c r="C31" s="12" t="n"/>
-      <c r="D31" s="12" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -5644,7 +8829,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>미네랄울 48K 50T</t>
+          <t>미네랄울 50K 50T</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -5693,9 +8878,6 @@
           <t>추정치 주의: f₀는 중공층 깊이와 면밀도로부터의 계산 추정값이며 실측 성적서가 아님. 내부 등급 비교 및 상담 설명 목적으로만 사용하고 대외 자료·견적서에 성능 수치로 기재하지 않음. 성능 보증이 필요한 현장은 시공 후 실측을 별도 항목으로 계상.</t>
         </is>
       </c>
-      <c r="B47" s="10" t="n"/>
-      <c r="C47" s="10" t="n"/>
-      <c r="D47" s="10" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -5754,7 +8936,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>목재 하지</t>
+          <t>목재 벽체틀</t>
         </is>
       </c>
     </row>
@@ -5778,17 +8960,17 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>미네랄울 보드</t>
+          <t>미네랄울 보온판 50K</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>48K · 50T</t>
+          <t>50K · 50T · 450×1000</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>KCC 또는 벽산 · 라이트필 031-604-3000</t>
+          <t>벽산 또는 KCC · 라이트필 031-604-3000</t>
         </is>
       </c>
     </row>
@@ -5868,7 +9050,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>판 두께 + 하지 물림</t>
+          <t>판 두께 + 벽체틀 물림</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -5985,7 +9167,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>하지 프레임 눕혀 짜기</t>
+          <t>벽체틀 눕혀 짜기</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -6442,14 +9624,14 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>돌차음판 4T + 이격 30(미네랄울 30T) + 투바이포 38×89(미네랄울 50T) + 일반석고 9.5T + 그린글루 + 차음석고 12.5T</t>
+          <t>돌차음판 4T + 이격 30(PET 25T 45K) + 투바이포 38×89(미네랄울 50T) + 일반석고 9.5T + 그린글루 + 차음석고 12.5T</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>하지 — LT (목재)</t>
+          <t>벽체틀 — LT (목재)</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -6461,7 +9643,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>하지 — LS (경량스터드)</t>
+          <t>벽체틀 — LS (경량스터드)</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -6502,7 +9684,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>미네랄울 48K 30T + 50T (합 80T)</t>
+          <t>PET 25T 45K(이격층) + 미네랄울 50K 50T(벽체틀층)</t>
         </is>
       </c>
     </row>
@@ -6538,7 +9720,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>돌차음판 4T 자착(구조체 면) · 상하부 런너 고무패드 3T · 사방 방음 실란트 · 미네랄울 48K</t>
+          <t>돌차음판 4T 자착(구조체 면) · 상하부 런너 고무패드 3T · 사방 방음 실란트 · 미네랄울 50K</t>
         </is>
       </c>
     </row>
@@ -6584,9 +9766,6 @@
           <t>L2 → L3은 시스템 전환입니다. 각재 뒷면 접촉이 사라지면서 지배 변수가 면밀도에서 중공층 거리로 바뀝니다. 저역이 처음으로 열리는 지점이며, 그린글루는 구조 전달이 끊긴 이 등급부터 의미를 가집니다.</t>
         </is>
       </c>
-      <c r="B29" s="18" t="n"/>
-      <c r="C29" s="18" t="n"/>
-      <c r="D29" s="18" t="n"/>
     </row>
     <row r="31" ht="56" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
@@ -6594,9 +9773,6 @@
           <t>충진재는 구조체 쪽에 붙입니다. 중공층 119mm에 100T를 넣으면 19mm 여유가 남습니다. 이 여유는 실내측 마감판 뒤에 두어야 하며, 재료가 판에 닿으면 그린글루 제진이 무효화됩니다.</t>
         </is>
       </c>
-      <c r="B31" s="12" t="n"/>
-      <c r="C31" s="12" t="n"/>
-      <c r="D31" s="12" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -6762,7 +9938,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>미네랄울 48K 30T + 50T (합 80T)</t>
+          <t>PET 25T 45K(이격층) + 미네랄울 50K 50T(벽체틀층)</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -6811,9 +9987,6 @@
           <t>추정치 주의: f₀는 중공층 깊이와 면밀도로부터의 계산 추정값이며 실측 성적서가 아님. 내부 등급 비교 및 상담 설명 목적으로만 사용하고 대외 자료·견적서에 성능 수치로 기재하지 않음. 성능 보증이 필요한 현장은 시공 후 실측을 별도 항목으로 계상.</t>
         </is>
       </c>
-      <c r="B48" s="10" t="n"/>
-      <c r="C48" s="10" t="n"/>
-      <c r="D48" s="10" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -6872,7 +10045,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>목재 하지</t>
+          <t>목재 벽체틀</t>
         </is>
       </c>
     </row>
@@ -6896,17 +10069,17 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>미네랄울 보드</t>
+          <t>PET 폴리에스터 흡음단열재</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>48K · 30T + 50T (합 80T)</t>
+          <t>45K · 25T · 1000×2000</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>KCC 또는 벽산 · 라이트필 031-604-3000</t>
+          <t>N25폴리 45K · KS F 5660 — 이격층 30mm, 미네랄울 최소 50T로 적용 불가</t>
         </is>
       </c>
     </row>
@@ -7003,7 +10176,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>판 두께 + 하지 물림</t>
+          <t>판 두께 + 벽체틀 물림</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -7105,7 +10278,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>하지 프레임 눕혀 짜기</t>
+          <t>벽체틀 눕혀 짜기</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -7120,7 +10293,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>하지 세우기</t>
+          <t>벽체틀 세우기</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -7135,7 +10308,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>미네랄울 30T</t>
+          <t>PET 25T 45K</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -7155,7 +10328,7 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>하지 안쪽 · 구조체 쪽으로 붙임</t>
+          <t>벽체틀 안쪽 · 구조체 쪽으로 붙임</t>
         </is>
       </c>
     </row>
@@ -7264,7 +10437,7 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>L3 최대 실패 요인. 시공 중 하지가 밀려 돌차음판에 닿으면 L2로 하락. 하부 런너 먹줄 확정 후 착수</t>
+          <t>L3 최대 실패 요인. 시공 중 벽체틀이 밀려 돌차음판에 닿으면 L2로 하락. 하부 런너 먹줄 확정 후 착수</t>
         </is>
       </c>
     </row>
@@ -7288,7 +10461,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>이격층 30mm에 30T, 하지층 89mm에 50T — 각 층 두께에 맞춰 배분. 이격층에 50T를 넣으면 20mm 압착이 발생하므로 금지</t>
+          <t>이격층 30mm에 30T, 벽체틀층 89mm에 50T — 각 층 두께에 맞춰 배분. 이격층에 50T를 넣으면 20mm 압착이 발생하므로 금지</t>
         </is>
       </c>
     </row>
@@ -7377,7 +10550,7 @@
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>하지가 돌차음판에 접촉</t>
+          <t>벽체틀이 돌차음판에 접촉</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
@@ -7623,7 +10796,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>하지 — LT (목재)</t>
+          <t>벽체틀 — LT (목재)</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -7635,7 +10808,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>하지 — LS (경량스터드)</t>
+          <t>벽체틀 — LS (경량스터드)</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -7676,7 +10849,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>미네랄울 48K 50T × 2</t>
+          <t>미네랄울 50K 50T × 2</t>
         </is>
       </c>
     </row>
@@ -7712,7 +10885,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>돌차음판 4T 자착(구조체 면) · 상하부 런너 고무패드 3T · 사방 방음 실란트 · 미네랄울 48K</t>
+          <t>돌차음판 4T 자착(구조체 면) · 상하부 런너 고무패드 3T · 사방 방음 실란트 · 미네랄울 50K</t>
         </is>
       </c>
     </row>
@@ -7758,9 +10931,6 @@
           <t>삼중벽으로 늘리지 않습니다. 판을 3장으로 만들면 공기층이 둘로 쪼개져 f₀가 두 개 생기고 둘 다 이중벽보다 높아집니다. 같은 두께에서 저역 성능이 15~20dB 나빠집니다. 두께 이상이 필요하면 AC-B(박스인박스)로 넘어갑니다.</t>
         </is>
       </c>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="10" t="n"/>
-      <c r="D29" s="10" t="n"/>
     </row>
     <row r="31" ht="56" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
@@ -7768,9 +10938,6 @@
           <t>지하철 · 기계실 인접 현장은 다른 문제입니다. 구조체 전체가 진동하는 조건에서는 그 위에 선 벽이 아무리 두꺼워도 함께 떨립니다. 벽 두께가 아니라 바닥 방진(F-L4 이상)과 6면 독립계가 답이며, 착공 전 슬래브 진동 실측이 선행되어야 합니다.</t>
         </is>
       </c>
-      <c r="B31" s="12" t="n"/>
-      <c r="C31" s="12" t="n"/>
-      <c r="D31" s="12" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -7936,7 +11103,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>미네랄울 48K 50T × 2</t>
+          <t>미네랄울 50K 50T × 2</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -7985,9 +11152,6 @@
           <t>추정치 주의: f₀는 중공층 깊이와 면밀도로부터의 계산 추정값이며 실측 성적서가 아님. 내부 등급 비교 및 상담 설명 목적으로만 사용하고 대외 자료·견적서에 성능 수치로 기재하지 않음. 성능 보증이 필요한 현장은 시공 후 실측을 별도 항목으로 계상.</t>
         </is>
       </c>
-      <c r="B48" s="10" t="n"/>
-      <c r="C48" s="10" t="n"/>
-      <c r="D48" s="10" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -8046,7 +11210,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>목재 하지</t>
+          <t>목재 벽체틀</t>
         </is>
       </c>
     </row>
@@ -8070,17 +11234,17 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>미네랄울 보드</t>
+          <t>미네랄울 보온판 50K</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>48K · 50T × 2</t>
+          <t>50K · 50T · 450×1000 × 2</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>KCC 또는 벽산 · 라이트필 031-604-3000</t>
+          <t>벽산 또는 KCC · 라이트필 031-604-3000</t>
         </is>
       </c>
     </row>
@@ -8177,7 +11341,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>판 두께 + 하지 물림</t>
+          <t>판 두께 + 벽체틀 물림</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -8279,7 +11443,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>하지 프레임 눕혀 짜기</t>
+          <t>벽체틀 눕혀 짜기</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -8294,7 +11458,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>하지 세우기</t>
+          <t>벽체틀 세우기</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -8329,7 +11493,7 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>하지 안쪽 · 구조체 쪽으로 붙임</t>
+          <t>벽체틀 안쪽 · 구조체 쪽으로 붙임</t>
         </is>
       </c>
     </row>
@@ -8544,7 +11708,7 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>수확체감 구간 · 하지 안정성 저하</t>
+          <t>수확체감 구간 · 벽체틀 안정성 저하</t>
         </is>
       </c>
     </row>
@@ -8563,7 +11727,7 @@
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>하지가 돌차음판에 접촉</t>
+          <t>벽체틀이 돌차음판에 접촉</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
@@ -8785,7 +11949,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>하지 — LT (목재)</t>
+          <t>벽체틀 — LT (목재)</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -8797,7 +11961,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>하지 — LS (경량스터드)</t>
+          <t>벽체틀 — LS (경량스터드)</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -8838,7 +12002,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>미네랄울 48K 50T × 2</t>
+          <t>미네랄울 50K 50T × 2</t>
         </is>
       </c>
     </row>
@@ -8874,7 +12038,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>돌차음판 4T 자착(구조체 면) · 상하부 런너 고무패드 3T · 사방 방음 실란트 · 미네랄울 48K</t>
+          <t>돌차음판 4T 자착(구조체 면) · 상하부 런너 고무패드 3T · 사방 방음 실란트 · 미네랄울 50K</t>
         </is>
       </c>
     </row>
@@ -8920,9 +12084,6 @@
           <t>L5는 AC-A(직접 시공)의 상한입니다. 이격 50mm, 충진 100T, 판 보강까지 모두 사용한 구성이며 그 이상은 두께로 해결되지 않습니다. 저역 확장이 아니라 전대역 마감의 성격이며, 더 필요하면 AC-B(박스인박스)로 계열이 바뀝니다.</t>
         </is>
       </c>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="10" t="n"/>
-      <c r="D29" s="10" t="n"/>
     </row>
     <row r="31" ht="56" customHeight="1">
       <c r="A31" s="17" t="inlineStr">
@@ -8930,9 +12091,6 @@
           <t>6면 등급 일치가 전제입니다. 벽 4면을 L5로 해도 바닥·천장이 낮으면 그쪽으로 나갑니다. 실 단위 등급(AC-R)으로 관리하며, F·C 시리즈가 동급 이상으로 따라오지 않으면 L5의 실효 성능은 L4에 머뭅니다.</t>
         </is>
       </c>
-      <c r="B31" s="18" t="n"/>
-      <c r="C31" s="18" t="n"/>
-      <c r="D31" s="18" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -9115,7 +12273,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>미네랄울 48K 50T × 2</t>
+          <t>미네랄울 50K 50T × 2</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -9164,9 +12322,6 @@
           <t>추정치 주의: f₀는 중공층 깊이와 면밀도로부터의 계산 추정값이며 실측 성적서가 아님. 내부 등급 비교 및 상담 설명 목적으로만 사용하고 대외 자료·견적서에 성능 수치로 기재하지 않음. 성능 보증이 필요한 현장은 시공 후 실측을 별도 항목으로 계상.</t>
         </is>
       </c>
-      <c r="B49" s="10" t="n"/>
-      <c r="C49" s="10" t="n"/>
-      <c r="D49" s="10" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -9225,7 +12380,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>목재 하지</t>
+          <t>목재 벽체틀</t>
         </is>
       </c>
     </row>
@@ -9249,17 +12404,17 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>미네랄울 보드</t>
+          <t>미네랄울 보온판 50K</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>48K · 50T × 2</t>
+          <t>50K · 50T · 450×1000 × 2</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>KCC 또는 벽산 · 라이트필 031-604-3000</t>
+          <t>벽산 또는 KCC · 라이트필 031-604-3000</t>
         </is>
       </c>
     </row>
@@ -9373,7 +12528,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>판 두께 + 하지 물림</t>
+          <t>판 두께 + 벽체틀 물림</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -9475,7 +12630,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>하지 프레임 눕혀 짜기</t>
+          <t>벽체틀 눕혀 짜기</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -9490,7 +12645,7 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>하지 세우기</t>
+          <t>벽체틀 세우기</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -9525,7 +12680,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>하지 안쪽 · 구조체 쪽으로 붙임</t>
+          <t>벽체틀 안쪽 · 구조체 쪽으로 붙임</t>
         </is>
       </c>
     </row>
@@ -9830,7 +12985,7 @@
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>단일 하지 칸막이</t>
+          <t>단일 벽체틀</t>
         </is>
       </c>
     </row>
@@ -9953,7 +13108,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>단일 하지 칸막이</t>
+          <t>단일 벽체틀</t>
         </is>
       </c>
     </row>
@@ -9972,7 +13127,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>하지 — LT (목재)</t>
+          <t>벽체틀 — LT (목재)</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -9984,7 +13139,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>하지 — LS (경량스터드)</t>
+          <t>벽체틀 — LS (경량스터드)</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -10025,7 +13180,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>미네랄울 48K 50T</t>
+          <t>미네랄울 50K 50T</t>
         </is>
       </c>
     </row>
@@ -10061,7 +13216,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>상하부 런너 고무패드 3T · 사방 방음 실란트 · 미네랄울 48K · 슬래브 도달 필수 · 양면 대칭</t>
+          <t>상하부 런너 고무패드 3T · 사방 방음 실란트 · 미네랄울 50K · 슬래브 도달 필수 · 양면 대칭</t>
         </is>
       </c>
     </row>
@@ -10107,9 +13262,6 @@
           <t>WS와 두께가 다른 이유. 구조벽면형은 기존 구조체가 이미 질량을 갖고 있어 한쪽만 보강하면 되지만, 칸막이는 0에서 시작해 양면을 모두 만들어야 합니다. 같은 등급에서 WP가 두꺼운 것은 성능이 아니라 출발점의 차이입니다.</t>
         </is>
       </c>
-      <c r="B29" s="12" t="n"/>
-      <c r="C29" s="12" t="n"/>
-      <c r="D29" s="12" t="n"/>
     </row>
     <row r="31" ht="56" customHeight="1">
       <c r="A31" s="17" t="inlineStr">
@@ -10117,9 +13269,6 @@
           <t>돌차음판은 WP에 쓰지 않습니다. 돌차음판은 기존 구조체 면의 공극을 덮고 면밀도를 올리는 자재입니다. 구조체가 없는 칸막이에는 붙일 자리가 없으며, L5에서만 마감판 사이 질량 보강재로 투입합니다.</t>
         </is>
       </c>
-      <c r="B31" s="18" t="n"/>
-      <c r="C31" s="18" t="n"/>
-      <c r="D31" s="18" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -10285,7 +13434,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>미네랄울 48K 50T</t>
+          <t>미네랄울 50K 50T</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -10334,9 +13483,6 @@
           <t>추정치 주의: f₀는 중공층 깊이와 면밀도로부터의 계산 추정값이며 실측 성적서가 아님. 내부 등급 비교 및 상담 설명 목적으로만 사용하고 대외 자료·견적서에 성능 수치로 기재하지 않음. 성능 보증이 필요한 현장은 시공 후 실측을 별도 항목으로 계상.</t>
         </is>
       </c>
-      <c r="B48" s="10" t="n"/>
-      <c r="C48" s="10" t="n"/>
-      <c r="D48" s="10" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -10378,7 +13524,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>목재 하지</t>
+          <t>목재 벽체틀</t>
         </is>
       </c>
     </row>
@@ -10402,17 +13548,17 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>미네랄울 보드</t>
+          <t>미네랄울 보온판 50K</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>48K · 50T</t>
+          <t>50K · 50T · 450×1000</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>KCC 또는 벽산 · 라이트필 031-604-3000</t>
+          <t>벽산 또는 KCC · 라이트필 031-604-3000</t>
         </is>
       </c>
     </row>
@@ -10492,7 +13638,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>판 두께 + 하지 물림</t>
+          <t>판 두께 + 벽체틀 물림</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -10564,7 +13710,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>하지 프레임 눕혀 짜기</t>
+          <t>벽체틀 눕혀 짜기</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -10579,7 +13725,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>하지 세우기</t>
+          <t>벽체틀 세우기</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -10786,7 +13932,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>배선·배관이 하지를 관통하는 위치를 판 부착 전에 확정. 사후 작업은 취약부를 만듦</t>
+          <t>배선·배관이 벽체틀을 관통하는 위치를 판 부착 전에 확정. 사후 작업은 취약부를 만듦</t>
         </is>
       </c>
     </row>
@@ -10919,7 +14065,7 @@
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>단일 하지 칸막이 (확대)</t>
+          <t>단일 벽체틀 (확대)</t>
         </is>
       </c>
     </row>
@@ -11042,7 +14188,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>단일 하지 칸막이 (확대)</t>
+          <t>단일 벽체틀 (확대)</t>
         </is>
       </c>
     </row>
@@ -11061,7 +14207,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>하지 — LT (목재)</t>
+          <t>벽체틀 — LT (목재)</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -11073,7 +14219,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>하지 — LS (경량스터드)</t>
+          <t>벽체틀 — LS (경량스터드)</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -11114,7 +14260,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>미네랄울 48K 50T × 2</t>
+          <t>미네랄울 50K 50T × 2</t>
         </is>
       </c>
     </row>
@@ -11150,7 +14296,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>상하부 런너 고무패드 3T · 사방 방음 실란트 · 미네랄울 48K · 슬래브 도달 필수 · 양면 대칭</t>
+          <t>상하부 런너 고무패드 3T · 사방 방음 실란트 · 미네랄울 50K · 슬래브 도달 필수 · 양면 대칭</t>
         </is>
       </c>
     </row>
@@ -11193,12 +14339,9 @@
     <row r="29" ht="56" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>단일 하지의 상한입니다. 중공층을 더 늘리려면 하지를 키워야 하는데, 스터드가 양면 판을 동시에 잡는 구조는 그대로입니다. L3에서 하지를 두 열로 분리하는 것이 다음 단계이며, 그것이 이 계열의 진짜 전환점입니다.</t>
-        </is>
-      </c>
-      <c r="B29" s="12" t="n"/>
-      <c r="C29" s="12" t="n"/>
-      <c r="D29" s="12" t="n"/>
+          <t>단일 벽체틀의 상한입니다. 중공층을 더 늘리려면 벽체틀을 키워야 하는데, 스터드가 양면 판을 동시에 잡는 구조는 그대로입니다. L3에서 벽체틀을 두 열로 분리하는 것이 다음 단계이며, 그것이 이 계열의 진짜 전환점입니다.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="56" customHeight="1">
       <c r="A31" s="9" t="inlineStr">
@@ -11206,9 +14349,6 @@
           <t>스태거드 스터드는 채택하지 않습니다. 넓은 런너에 스터드를 엇갈려 세우면 두께를 아낄 수 있으나, 프레임을 바닥에서 눕혀 짤 수 없어 스터드를 하나씩 세우며 빗각 타카로 고정해야 합니다. 공수가 배로 늘고 정밀도가 떨어져 표준에서 제외합니다.</t>
         </is>
       </c>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
-      <c r="D31" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -11374,7 +14514,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>미네랄울 48K 50T × 2</t>
+          <t>미네랄울 50K 50T × 2</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -11423,9 +14563,6 @@
           <t>추정치 주의: f₀는 중공층 깊이와 면밀도로부터의 계산 추정값이며 실측 성적서가 아님. 내부 등급 비교 및 상담 설명 목적으로만 사용하고 대외 자료·견적서에 성능 수치로 기재하지 않음. 성능 보증이 필요한 현장은 시공 후 실측을 별도 항목으로 계상.</t>
         </is>
       </c>
-      <c r="B48" s="10" t="n"/>
-      <c r="C48" s="10" t="n"/>
-      <c r="D48" s="10" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -11467,7 +14604,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>목재 하지</t>
+          <t>목재 벽체틀</t>
         </is>
       </c>
     </row>
@@ -11491,17 +14628,17 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>미네랄울 보드</t>
+          <t>미네랄울 보온판 50K</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>48K · 50T × 2</t>
+          <t>50K · 50T · 450×1000 × 2</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>KCC 또는 벽산 · 라이트필 031-604-3000</t>
+          <t>벽산 또는 KCC · 라이트필 031-604-3000</t>
         </is>
       </c>
     </row>
@@ -11581,7 +14718,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>판 두께 + 하지 물림</t>
+          <t>판 두께 + 벽체틀 물림</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -11653,7 +14790,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>하지 프레임 눕혀 짜기</t>
+          <t>벽체틀 눕혀 짜기</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -11668,7 +14805,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>하지 세우기</t>
+          <t>벽체틀 세우기</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -11827,7 +14964,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>L1(89mm) 대비 f₀ 약 116 → 93Hz. 단일 하지에서 가능한 최대 중공층</t>
+          <t>L1(89mm) 대비 f₀ 약 116 → 93Hz. 단일 벽체틀에서 가능한 최대 중공층</t>
         </is>
       </c>
     </row>
@@ -11846,12 +14983,12 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>단일 하지의 한계</t>
+          <t>단일 벽체틀의 한계</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>스터드 하나가 양면 판을 동시에 잡고 있어 판을 아무리 무겁게 해도 스터드 관통 전달이 남음. 이 경로를 끊는 것이 L3(이중 하지)</t>
+          <t>스터드 하나가 양면 판을 동시에 잡고 있어 판을 아무리 무겁게 해도 스터드 관통 전달이 남음. 이 경로를 끊는 것이 L3(이중 벽체틀)</t>
         </is>
       </c>
     </row>
@@ -12008,7 +15145,7 @@
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>이중 하지 칸막이</t>
+          <t>이중 벽체틀</t>
         </is>
       </c>
     </row>
@@ -12131,7 +15268,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>이중 하지 칸막이</t>
+          <t>이중 벽체틀</t>
         </is>
       </c>
     </row>
@@ -12150,7 +15287,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>하지 — LT (목재)</t>
+          <t>벽체틀 — LT (목재)</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -12162,7 +15299,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>하지 — LS (경량스터드)</t>
+          <t>벽체틀 — LS (경량스터드)</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -12203,7 +15340,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>미네랄울 48K 50T × 2</t>
+          <t>미네랄울 50K 50T × 2</t>
         </is>
       </c>
     </row>
@@ -12239,7 +15376,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>상하부 런너 고무패드 3T · 사방 방음 실란트 · 미네랄울 48K · 슬래브 도달 필수 · 양면 대칭</t>
+          <t>상하부 런너 고무패드 3T · 사방 방음 실란트 · 미네랄울 50K · 슬래브 도달 필수 · 양면 대칭</t>
         </is>
       </c>
     </row>
@@ -12282,12 +15419,9 @@
     <row r="29" ht="56" customHeight="1">
       <c r="A29" s="17" t="inlineStr">
         <is>
-          <t>L2 → L3이 이 계열의 전환점입니다. 단일 하지에서는 스터드가 양면 판을 동시에 잡아 판을 아무리 무겁게 해도 관통 전달이 남습니다. 두 열로 나누면 그 경로가 사라지고, 남는 것은 상·하부 런너뿐입니다.</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="n"/>
-      <c r="C29" s="18" t="n"/>
-      <c r="D29" s="18" t="n"/>
+          <t>L2 → L3이 이 계열의 전환점입니다. 단일 벽체틀에서는 스터드가 양면 판을 동시에 잡아 판을 아무리 무겁게 해도 관통 전달이 남습니다. 두 열로 나누면 그 경로가 사라지고, 남는 것은 상·하부 런너뿐입니다.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="56" customHeight="1">
       <c r="A31" s="9" t="inlineStr">
@@ -12295,9 +15429,6 @@
           <t>분리 30mm에 무엇도 걸치면 안 됩니다. 전선 하나, 목재 조각 하나, 압착된 미네랄울 한 곳이면 이중벽이 단일벽으로 돌아갑니다. 시공 전 전기·설비 협의를 반드시 선행하고, 판 부착 직전에 전수 확인합니다.</t>
         </is>
       </c>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
-      <c r="D31" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -12480,7 +15611,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>미네랄울 48K 50T × 2</t>
+          <t>미네랄울 50K 50T × 2</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -12529,9 +15660,6 @@
           <t>추정치 주의: f₀는 중공층 깊이와 면밀도로부터의 계산 추정값이며 실측 성적서가 아님. 내부 등급 비교 및 상담 설명 목적으로만 사용하고 대외 자료·견적서에 성능 수치로 기재하지 않음. 성능 보증이 필요한 현장은 시공 후 실측을 별도 항목으로 계상.</t>
         </is>
       </c>
-      <c r="B49" s="10" t="n"/>
-      <c r="C49" s="10" t="n"/>
-      <c r="D49" s="10" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -12573,7 +15701,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>목재 하지</t>
+          <t>목재 벽체틀</t>
         </is>
       </c>
     </row>
@@ -12597,17 +15725,17 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>미네랄울 보드</t>
+          <t>미네랄울 보온판 50K</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>48K · 50T × 2</t>
+          <t>50K · 50T · 450×1000 × 2</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>KCC 또는 벽산 · 라이트필 031-604-3000</t>
+          <t>벽산 또는 KCC · 라이트필 031-604-3000</t>
         </is>
       </c>
     </row>
@@ -12704,7 +15832,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>판 두께 + 하지 물림</t>
+          <t>판 두께 + 벽체틀 물림</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
